--- a/stories/arbres/TREE-LAN-003.xlsx
+++ b/stories/arbres/TREE-LAN-003.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Léa est à la maison, avec maman. Dehors, la pluie. Ploc ploc. Maman dit : un son. Le nom, c'est la pluie. Un train passe au loin. Tchou. Un son. Le nom, c'est le train. Le chat miaule. Un son. Le nom, c'est le chat. Léa écoute. Son. Nom. On entend un son. On dit son nom.</t>
+          <t>Léa est à la maison, avec maman. Dehors, la pluie. Ploc ploc. Un son. Le nom, c'est la pluie. Un train passe au loin. Tchou. Un son. Le nom, c'est le train. Le chat miaule. Un son. Le nom, c'est le chat. Léa écoute. Son. Nom. On entend un son. On dit son nom.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Léa est à la maison, avec maman. Dehors, la pluie. Ploc ploc.
+maman|Un son.
+narrateur|Le nom, c'est la pluie. Un train passe au loin. Tchou. Un son. Le nom, c'est le train. Le chat miaule. Un son. Le nom, c'est le chat. Léa écoute. Son. Nom. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|C'est le matin. Un oiseau. Cui cui. Un son. Le nom : oiseau. Léa dit le nom. Maman sourit. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1829,6 +1863,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Ploc ploc. C'est le son de quoi ?</t>
         </is>
       </c>
     </row>
@@ -1997,6 +2036,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Léa a entendu un son. Léa a dit le nom. Pluie. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2183,6 +2227,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2345,6 +2394,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la cuisine. Une cloche tinte au loin. Dans la cuisine, une cuillère. Ting. Un son. Le nom : cuillère. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2531,6 +2585,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2693,6 +2752,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le ballon rouge tout près. La lumière est claire. On referme le sac. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2855,6 +2919,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3017,6 +3086,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le seau bleu tout près. Des miettes dorment sur la table. On essuie une miette. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Maman serre Léa tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3179,6 +3253,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3341,6 +3420,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le doudou tout près. Un chat miaule une fois. On met le doudou près. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3503,6 +3587,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3665,6 +3754,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le jardin. La terre est un peu humide. Dans le jardin, un oiseau. Un son. Le nom : oiseau. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3851,6 +3945,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -3875,7 +3974,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Léa garde le ballon rouge tout près. Les chaussures font toc toc. On lace les chaussures. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Léa range. Maman dit : c'est bien.</t>
+          <t>Léa garde le ballon rouge tout près. Les chaussures font toc toc. On lace les chaussures. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Léa range. C'est bien.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4013,6 +4112,12 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le ballon rouge tout près. Les chaussures font toc toc. On lace les chaussures. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Léa range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4175,6 +4280,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4337,6 +4447,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le seau bleu tout près. La couverture est douce. On met le manteau. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. On souffle. Léa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4499,6 +4614,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4661,6 +4781,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le doudou tout près. Une cloche tinte au loin. On boit une gorgée. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Léa prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4823,6 +4948,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4985,6 +5115,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la chambre. Un chat miaule une fois. Dans la chambre, le doudou ne fait pas de son. Dehors, la pluie. Son. Nom. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5171,6 +5306,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5333,6 +5473,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le ballon rouge tout près. Le bois sent le chaud. On feuillette le livre. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5495,6 +5640,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5657,6 +5807,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le seau bleu tout près. Une goutte tombe, ploc. On referme le livre. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Maman serre Léa tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5819,6 +5974,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5981,6 +6141,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le doudou tout près. Le savon sent la fleur. On pose le ballon. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6143,6 +6308,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6167,7 +6337,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Après la sieste, l'eau du robinet. Un son. Le nom : l'eau. Léa dit : eau. Son. Nom. On entend un son. On dit son nom.</t>
+          <t>Après la sieste, l'eau du robinet. Un son. Le nom : l'eau. Eau. Son. Nom. On entend un son. On dit son nom.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6305,6 +6475,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Après la sieste, l'eau du robinet. Un son. Le nom : l'eau.
+enfant-f|Eau. Son. Nom. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6485,6 +6661,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Tchou tchou. Quel nom ?</t>
         </is>
       </c>
     </row>
@@ -6653,6 +6834,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Son. Nom. Train. Léa a reconnu. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6839,6 +7025,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7001,6 +7192,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la cuisine. Le savon sent la fleur. Ça sent le pain. Le four fait un petit son. Léa dit un nom. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7187,6 +7383,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7211,7 +7412,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Léa garde le ballon rouge tout près. Le tissu est tout doux. On secoue le sable. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Léa range. Maman dit : c'est bien.</t>
+          <t>Léa garde le ballon rouge tout près. Le tissu est tout doux. On secoue le sable. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Léa range. C'est bien.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7349,6 +7550,12 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le ballon rouge tout près. Le tissu est tout doux. On secoue le sable. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Léa range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7511,6 +7718,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7673,6 +7885,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le seau bleu tout près. Une cuillère tinte. On caresse le tissu. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. On souffle. Léa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7835,6 +8052,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7997,6 +8219,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le doudou tout près. Le sable est tiède. On tend la main. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Léa prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8159,6 +8386,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8321,6 +8553,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le jardin. Un grelot sonne. Le vent. Un son. Le nom : vent. Léa écoute. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8507,6 +8744,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8669,6 +8911,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le ballon rouge tout près. Un rire court, tout petit. On chante un petit air. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8831,6 +9078,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8993,6 +9245,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le seau bleu tout près. Le papier froisse, chut. On compte jusqu'à trois. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Maman serre Léa tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9155,6 +9412,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9317,6 +9579,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le doudou tout près. L'herbe chatouille le mollet. On montre du doigt. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9479,6 +9746,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9641,6 +9913,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la chambre. Le vent est doux sur la joue. On referme un livre. Un son. Le nom : livre. Léa nomme. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9827,6 +10104,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9851,7 +10133,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Léa garde le ballon rouge tout près. Un pigeon roucoule. On range la chaise. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Léa range. Maman dit : c'est bien.</t>
+          <t>Léa garde le ballon rouge tout près. Un pigeon roucoule. On range la chaise. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Léa range. C'est bien.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -9989,6 +10271,12 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le ballon rouge tout près. Un pigeon roucoule. On range la chaise. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Léa range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10151,6 +10439,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10313,6 +10606,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le seau bleu tout près. La fenêtre vibre un peu. On range un objet. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. On souffle. Léa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10475,6 +10773,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10637,6 +10940,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le doudou tout près. Le lait est froid dans le verre. On se tient la main. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Léa prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10799,6 +11107,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10961,6 +11274,11 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Le soir, le chat encore. Miaou. Un son. Le nom : chat. Léa nomme le son. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11141,6 +11459,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Miaou. C'est quel nom ?</t>
         </is>
       </c>
     </row>
@@ -11309,6 +11632,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Chat. Un son. Un nom. Maman confirme. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11495,6 +11823,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11657,6 +11990,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la cuisine. Un pigeon roucoule. L'eau coule. Son. Nom : eau. Léa répète. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11843,6 +12181,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12005,6 +12348,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le ballon rouge tout près. La corde du sac est rêche. On dit merci. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12167,6 +12515,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12329,6 +12682,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le seau bleu tout près. Le savon mousse entre les doigts. On souffle doucement. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Maman serre Léa tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12491,6 +12849,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12653,6 +13016,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le doudou tout près. Un ruisseau chante. On écoute jusqu'au bout. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12815,6 +13183,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12977,6 +13350,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers le jardin. L'eau fait un petit bruit. Un pigeon. Roucoule. Un son. Le nom : pigeon. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13163,6 +13541,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13187,7 +13570,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Léa garde le ballon rouge tout près. La laine gratte un peu. On attend son tour. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Léa range. Maman dit : c'est bien.</t>
+          <t>Léa garde le ballon rouge tout près. La laine gratte un peu. On attend son tour. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Léa range. C'est bien.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13325,6 +13708,12 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le ballon rouge tout près. La laine gratte un peu. On attend son tour. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Léa range.
+maman|C'est bien.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13487,6 +13876,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13649,6 +14043,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le seau bleu tout près. Un pain croustille. On sourit ensemble. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. On souffle. Léa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13811,6 +14210,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13973,6 +14377,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le doudou tout près. Le savon glisse. On pose les pieds par terre. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Léa prend la main de maman.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14135,6 +14544,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14159,7 +14573,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Léa va vers la chambre. La fenêtre vibre un peu. Le chat encore. Son. Nom. Léa dit : chat. On entend un son. On dit son nom.</t>
+          <t>Léa va vers la chambre. La fenêtre vibre un peu. Le chat encore. Son. Nom. Chat. On entend un son. On dit son nom.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14297,6 +14711,12 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Léa va vers la chambre. La fenêtre vibre un peu. Le chat encore. Son. Nom.
+enfant-f|Chat. On entend un son. On dit son nom.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14483,6 +14903,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14645,6 +15070,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le ballon rouge tout près. Une plume vole. On parle tout bas. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. Léa dit merci à maman. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14807,6 +15237,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14969,6 +15404,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le seau bleu tout près. Le banc est lisse. On range les jouets. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Maman serre Léa tout doux.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15131,6 +15571,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15293,6 +15738,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Léa garde le doudou tout près. Un grelot sonne. On s'assoit un moment. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. Papa n'est pas loin. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15455,6 +15905,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15473,7 +15928,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15490,6 +15945,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-LAN-003.xlsx
+++ b/stories/arbres/TREE-LAN-003.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Le nom, c'est la pluie. Un train passe au loin. Tchou. Un son. Le nom, c'est le train. Le chat miaule. Un son. Le nom, c'est le chat. Léa écoute. Son. Nom. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
           <t>narrateur|C'est le matin. Un oiseau. Cui cui. Un son. Le nom : oiseau. Léa dit le nom. Maman sourit. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1870,6 +1878,7 @@
           <t>narrateur|Ploc ploc. C'est le son de quoi ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2041,6 +2050,7 @@
           <t>narrateur|Léa a entendu un son. Léa a dit le nom. Pluie. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2232,6 +2242,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2399,6 +2410,7 @@
           <t>narrateur|Léa va vers la cuisine. Une cloche tinte au loin. Dans la cuisine, une cuillère. Ting. Un son. Le nom : cuillère. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2590,6 +2602,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2757,6 +2770,7 @@
           <t>narrateur|Léa garde le ballon rouge tout près. La lumière est claire. On referme le sac. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2924,6 +2938,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3091,6 +3106,7 @@
           <t>narrateur|Léa garde le seau bleu tout près. Des miettes dorment sur la table. On essuie une miette. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Maman serre Léa tout doux.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3258,6 +3274,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3425,6 +3442,7 @@
           <t>narrateur|Léa garde le doudou tout près. Un chat miaule une fois. On met le doudou près. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3592,6 +3610,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3759,6 +3778,7 @@
           <t>narrateur|Léa va vers le jardin. La terre est un peu humide. Dans le jardin, un oiseau. Un son. Le nom : oiseau. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3950,6 +3970,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4118,6 +4139,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4285,6 +4307,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4452,6 +4475,7 @@
           <t>narrateur|Léa garde le seau bleu tout près. La couverture est douce. On met le manteau. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. On souffle. Léa sourit.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4619,6 +4643,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4786,6 +4811,7 @@
           <t>narrateur|Léa garde le doudou tout près. Une cloche tinte au loin. On boit une gorgée. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Léa prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4953,6 +4979,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5120,6 +5147,7 @@
           <t>narrateur|Léa va vers la chambre. Un chat miaule une fois. Dans la chambre, le doudou ne fait pas de son. Dehors, la pluie. Son. Nom. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5311,6 +5339,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5478,6 +5507,7 @@
           <t>narrateur|Léa garde le ballon rouge tout près. Le bois sent le chaud. On feuillette le livre. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5645,6 +5675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5812,6 +5843,7 @@
           <t>narrateur|Léa garde le seau bleu tout près. Une goutte tombe, ploc. On referme le livre. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Maman serre Léa tout doux.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5979,6 +6011,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6146,6 +6179,7 @@
           <t>narrateur|Léa garde le doudou tout près. Le savon sent la fleur. On pose le ballon. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6313,6 +6347,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6481,6 +6516,7 @@
 enfant-f|Eau. Son. Nom. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6668,6 +6704,7 @@
           <t>narrateur|Tchou tchou. Quel nom ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6839,6 +6876,7 @@
           <t>narrateur|Son. Nom. Train. Léa a reconnu. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7030,6 +7068,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7197,6 +7236,7 @@
           <t>narrateur|Léa va vers la cuisine. Le savon sent la fleur. Ça sent le pain. Le four fait un petit son. Léa dit un nom. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7388,6 +7428,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7556,6 +7597,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7723,6 +7765,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7890,6 +7933,7 @@
           <t>narrateur|Léa garde le seau bleu tout près. Une cuillère tinte. On caresse le tissu. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. On souffle. Léa sourit.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8057,6 +8101,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8224,6 +8269,7 @@
           <t>narrateur|Léa garde le doudou tout près. Le sable est tiède. On tend la main. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Léa prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8391,6 +8437,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8558,6 +8605,7 @@
           <t>narrateur|Léa va vers le jardin. Un grelot sonne. Le vent. Un son. Le nom : vent. Léa écoute. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8749,6 +8797,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8916,6 +8965,7 @@
           <t>narrateur|Léa garde le ballon rouge tout près. Un rire court, tout petit. On chante un petit air. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9083,6 +9133,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9250,6 +9301,7 @@
           <t>narrateur|Léa garde le seau bleu tout près. Le papier froisse, chut. On compte jusqu'à trois. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Maman serre Léa tout doux.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9417,6 +9469,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9584,6 +9637,7 @@
           <t>narrateur|Léa garde le doudou tout près. L'herbe chatouille le mollet. On montre du doigt. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9751,6 +9805,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9918,6 +9973,7 @@
           <t>narrateur|Léa va vers la chambre. Le vent est doux sur la joue. On referme un livre. Un son. Le nom : livre. Léa nomme. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10109,6 +10165,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10277,6 +10334,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10444,6 +10502,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10611,6 +10670,7 @@
           <t>narrateur|Léa garde le seau bleu tout près. La fenêtre vibre un peu. On range un objet. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. On souffle. Léa sourit.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10778,6 +10838,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10945,6 +11006,7 @@
           <t>narrateur|Léa garde le doudou tout près. Le lait est froid dans le verre. On se tient la main. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Léa prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11112,6 +11174,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11279,6 +11342,7 @@
           <t>narrateur|Le soir, le chat encore. Miaou. Un son. Le nom : chat. Léa nomme le son. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11466,6 +11530,7 @@
           <t>narrateur|Miaou. C'est quel nom ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11637,6 +11702,7 @@
           <t>narrateur|Chat. Un son. Un nom. Maman confirme. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11828,6 +11894,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11995,6 +12062,7 @@
           <t>narrateur|Léa va vers la cuisine. Un pigeon roucoule. L'eau coule. Son. Nom : eau. Léa répète. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12186,6 +12254,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12353,6 +12422,7 @@
           <t>narrateur|Léa garde le ballon rouge tout près. La corde du sac est rêche. On dit merci. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12520,6 +12590,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12687,6 +12758,7 @@
           <t>narrateur|Léa garde le seau bleu tout près. Le savon mousse entre les doigts. On souffle doucement. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Maman serre Léa tout doux.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12854,6 +12926,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13021,6 +13094,7 @@
           <t>narrateur|Léa garde le doudou tout près. Un ruisseau chante. On écoute jusqu'au bout. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13188,6 +13262,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13355,6 +13430,7 @@
           <t>narrateur|Léa va vers le jardin. L'eau fait un petit bruit. Un pigeon. Roucoule. Un son. Le nom : pigeon. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13546,6 +13622,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13714,6 +13791,7 @@
 maman|C'est bien.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13881,6 +13959,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14048,6 +14127,7 @@
           <t>narrateur|Léa garde le seau bleu tout près. Un pain croustille. On sourit ensemble. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. On souffle. Léa sourit.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14215,6 +14295,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14382,6 +14463,7 @@
           <t>narrateur|Léa garde le doudou tout près. Le savon glisse. On pose les pieds par terre. On a entendu un son. On a dit son nom. Les oreilles ont écouté. On entend un son. On dit son nom. Léa prend la main de maman.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14549,6 +14631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14717,6 +14800,7 @@
 enfant-f|Chat. On entend un son. On dit son nom.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14908,6 +14992,7 @@
           <t>narrateur|On peut prendre le ballon rouge, le seau bleu, ou le doudou.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15075,6 +15160,7 @@
           <t>narrateur|Léa garde le ballon rouge tout près. Une plume vole. On parle tout bas. On a entendu un son. On a dit son nom. La pluie continue. On entend un son. On dit son nom. Léa dit merci à maman. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15242,6 +15328,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15409,6 +15496,7 @@
           <t>narrateur|Léa garde le seau bleu tout près. Le banc est lisse. On range les jouets. On a entendu un son. On a dit son nom. Le train s'éloigne. On entend un son. On dit son nom. Maman serre Léa tout doux.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15576,6 +15664,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15743,6 +15832,7 @@
           <t>narrateur|Léa garde le doudou tout près. Un grelot sonne. On s'assoit un moment. On a entendu un son. On a dit son nom. Le chat se tait. On entend un son. On dit son nom. Papa n'est pas loin. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15910,6 +16000,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15928,7 +16019,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15952,6 +16043,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15966,7 +16071,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16153,6 +16258,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
